--- a/results/04-2026/04.30 no_obbba/beta/inputs-04-2026.xlsx
+++ b/results/04-2026/04.30 no_obbba/beta/inputs-04-2026.xlsx
@@ -5081,7 +5081,7 @@
         <v>2684.09748115581</v>
       </c>
       <c r="S29" t="n">
-        <v>458.194986454526</v>
+        <v>488.194986454526</v>
       </c>
       <c r="T29" t="n">
         <v>162.643016309613</v>
@@ -5138,7 +5138,7 @@
         <v>-1556.54023218234</v>
       </c>
       <c r="AL29" t="n">
-        <v>-172.585095282328</v>
+        <v>-173.585095282328</v>
       </c>
       <c r="AM29" t="n">
         <v>-70.9432727516778</v>
@@ -5239,7 +5239,7 @@
         <v>2709.61779256644</v>
       </c>
       <c r="S30" t="n">
-        <v>462.478271406646</v>
+        <v>492.758716527964</v>
       </c>
       <c r="T30" t="n">
         <v>143.140105616203</v>
@@ -5296,7 +5296,7 @@
         <v>-1574.72016081599</v>
       </c>
       <c r="AL30" t="n">
-        <v>-172.257704329216</v>
+        <v>-174.267052499927</v>
       </c>
       <c r="AM30" t="n">
         <v>-71.1937227740491</v>
@@ -5397,7 +5397,7 @@
         <v>2735.18355114505</v>
       </c>
       <c r="S31" t="n">
-        <v>466.8015972377</v>
+        <v>497.365109129205</v>
       </c>
       <c r="T31" t="n">
         <v>115.322937925207</v>
@@ -5454,7 +5454,7 @@
         <v>-1592.46633808405</v>
       </c>
       <c r="AL31" t="n">
-        <v>-171.307757570473</v>
+        <v>-174.3358894709</v>
       </c>
       <c r="AM31" t="n">
         <v>-71.5336735570469</v>
@@ -5555,7 +5555,7 @@
         <v>2761.80377090598</v>
       </c>
       <c r="S32" t="n">
-        <v>471.165338256661</v>
+        <v>502.014563074843</v>
       </c>
       <c r="T32" t="n">
         <v>85.0823596752584</v>
@@ -5612,7 +5612,7 @@
         <v>-1609.88972303878</v>
       </c>
       <c r="AL32" t="n">
-        <v>-170.659935512362</v>
+        <v>-174.716374906729</v>
       </c>
       <c r="AM32" t="n">
         <v>-71.8826222818791</v>
@@ -5713,7 +5713,7 @@
         <v>2788.75455279793</v>
       </c>
       <c r="S33" t="n">
-        <v>475.569872271603</v>
+        <v>506.707480909676</v>
       </c>
       <c r="T33" t="n">
         <v>50.6890505411461</v>
@@ -5770,7 +5770,7 @@
         <v>-1626.31325630583</v>
       </c>
       <c r="AL33" t="n">
-        <v>-169.558931254748</v>
+        <v>-174.653290937051</v>
       </c>
       <c r="AM33" t="n">
         <v>-72.1367489038031</v>
@@ -5871,7 +5871,7 @@
         <v>2816.33443957647</v>
       </c>
       <c r="S34" t="n">
-        <v>480.015580622418</v>
+        <v>511.444268941559</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>-1643.00316280064</v>
       </c>
       <c r="AL34" t="n">
-        <v>-169.919450608829</v>
+        <v>-176.061433235103</v>
       </c>
       <c r="AM34" t="n">
         <v>-72.041206263982</v>
